--- a/data/2024/28-mures/114319-targu-mures/budget_file.xlsx
+++ b/data/2024/28-mures/114319-targu-mures/budget_file.xlsx
@@ -2639,7 +2639,7 @@
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
-      <c r="C70" s="2" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>Vărsăminte din secţiunea de funcţionare pentru finanţarea secţiunii de dezvoltare a bugetului local (cu semnul minus)</t>
         </is>
@@ -2647,11 +2647,7 @@
       <c r="E70" t="n">
         <v>3</v>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F70" t="inlineStr"/>
       <c r="G70" s="3" t="n">
         <v>-18788732</v>
       </c>
@@ -2665,7 +2661,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="C71" s="2" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>Vărsăminte din secţiunea de funcţionare</t>
         </is>
@@ -2673,11 +2669,7 @@
       <c r="E71" t="n">
         <v>3</v>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" s="3" t="n">
         <v>18788732</v>
       </c>
@@ -3322,7 +3314,7 @@
       </c>
     </row>
     <row r="93" ht="30" customHeight="1">
-      <c r="C93" s="2" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>Subventii acordate in baza contractelor de parteneriat sau asociere, pentru sectiunea de functionare</t>
         </is>
@@ -3330,11 +3322,7 @@
       <c r="E93" t="n">
         <v>4</v>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" s="3" t="n">
         <v>689000</v>
       </c>
@@ -3474,7 +3462,7 @@
       </c>
       <c r="J97" s="8" t="inlineStr">
         <is>
-          <t>49.02 credite_restante: parent 826.705.000,00 != sum(children) 306.782.000,00 (2 children); 49.02 total_2024: parent 604.574.000,00 != sum(children) 85.019.000,00 (2 children)</t>
+          <t>49.02 total_2024: parent 604.574.000,00 != sum(children) 85.019.000,00 (2 children); 49.02 credite_restante: parent 826.705.000,00 != sum(children) 306.782.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6252,7 @@
       </c>
       <c r="J175" s="8" t="inlineStr">
         <is>
-          <t>61.02 credite_restante: parent 617.000,00 != sum(children) 600.000,00 (1 children); 61.02 total_2024: parent 24.323.000,00 != sum(children) 1.064.000,00 (1 children)</t>
+          <t>61.02 total_2024: parent 24.323.000,00 != sum(children) 1.064.000,00 (1 children); 61.02 credite_restante: parent 617.000,00 != sum(children) 600.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6722,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="C189" s="2" t="inlineStr">
+      <c r="C189" s="7" t="inlineStr">
         <is>
           <t>Directia Politia Locala</t>
         </is>
@@ -6742,11 +6730,7 @@
       <c r="E189" t="n">
         <v>6</v>
       </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F189" t="inlineStr"/>
       <c r="G189" s="3" t="n">
         <v>22425000</v>
       </c>
@@ -6855,7 +6839,7 @@
       </c>
       <c r="J192" s="8" t="inlineStr">
         <is>
-          <t>65.02 total_2024: parent 88.907.000,00 != sum(children) 1.097.000,00 (1 children); 65.02 credite_restante: parent 169.303.000,00 != sum(children) 34.950.000,00 (1 children); 65.02 total_2024: parent 88.907.000,00 != sum(children) 9.123.000,00 (1 children)</t>
+          <t>65.02 total_2024: parent 88.907.000,00 != sum(children) 1.097.000,00 (1 children); 65.02 total_2024: parent 88.907.000,00 != sum(children) 9.123.000,00 (1 children); 65.02 credite_restante: parent 169.303.000,00 != sum(children) 34.950.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -10482,7 +10466,7 @@
       </c>
       <c r="J295" s="8" t="inlineStr">
         <is>
-          <t>70.02 credite_restante: parent 275.712.000,00 != sum(children) 211.955.000,00 (1 children); 70.02 total_2024: parent 95.045.000,00 != sum(children) 30.658.000,00 (1 children)</t>
+          <t>70.02 total_2024: parent 95.045.000,00 != sum(children) 30.658.000,00 (1 children); 70.02 credite_restante: parent 275.712.000,00 != sum(children) 211.955.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11499,7 @@
       </c>
     </row>
     <row r="325" ht="30" customHeight="1">
-      <c r="C325" s="2" t="inlineStr">
+      <c r="C325" s="7" t="inlineStr">
         <is>
           <t>7002500102 Administratia Gradinii Zoologice si a Platoului Cornesti</t>
         </is>
@@ -11523,11 +11507,7 @@
       <c r="E325" t="n">
         <v>10</v>
       </c>
-      <c r="F325" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F325" t="inlineStr"/>
       <c r="G325" s="3" t="n">
         <v>12277000</v>
       </c>
@@ -11802,7 +11782,7 @@
       </c>
       <c r="J332" s="8" t="inlineStr">
         <is>
-          <t>74.02 credite_restante: parent 162.000.000,00 != sum(children) 2.000.000,00 (1 children); 74.02 total_2024: parent 59.308.000,00 != sum(children) 1.500.000,00 (1 children)</t>
+          <t>74.02 total_2024: parent 59.308.000,00 != sum(children) 1.500.000,00 (1 children); 74.02 credite_restante: parent 162.000.000,00 != sum(children) 2.000.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12370,7 @@
       </c>
       <c r="J349" s="8" t="inlineStr">
         <is>
-          <t>84.02 credite_restante: parent 215.048.000,00 != sum(children) 55.912.000,00 (2 children); 84.02 total_2024: parent 121.708.000,00 != sum(children) 31.465.000,00 (2 children)</t>
+          <t>84.02 total_2024: parent 121.708.000,00 != sum(children) 31.465.000,00 (2 children); 84.02 credite_restante: parent 215.048.000,00 != sum(children) 55.912.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -13294,7 +13274,7 @@
       </c>
       <c r="J374" s="8" t="inlineStr">
         <is>
-          <t>84.02.03 credite_restante: parent 215.048.000,00 != sum(children) 77.040.000,00 (1 children); 84.02.03 total_2024: parent 121.708.000,00 != sum(children) 50.117.000,00 (1 children)</t>
+          <t>84.02.03 total_2024: parent 121.708.000,00 != sum(children) 50.117.000,00 (1 children); 84.02.03 credite_restante: parent 215.048.000,00 != sum(children) 77.040.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13310,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="C376" s="2" t="inlineStr">
+      <c r="C376" s="7" t="inlineStr">
         <is>
           <t>Strazi Directia Tehnica</t>
         </is>
@@ -13338,11 +13318,7 @@
       <c r="E376" t="n">
         <v>11</v>
       </c>
-      <c r="F376" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F376" t="inlineStr"/>
       <c r="G376" s="3" t="n">
         <v>39702000</v>
       </c>
@@ -13356,7 +13332,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="C377" s="2" t="inlineStr">
+      <c r="C377" s="7" t="inlineStr">
         <is>
           <t>Strazi ADP</t>
         </is>
@@ -13364,11 +13340,7 @@
       <c r="E377" t="n">
         <v>11</v>
       </c>
-      <c r="F377" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F377" t="inlineStr"/>
       <c r="G377" s="3" t="n">
         <v>31599000</v>
       </c>
@@ -13382,7 +13354,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="C378" s="2" t="inlineStr">
+      <c r="C378" s="7" t="inlineStr">
         <is>
           <t>Biroul parcari, garaje si ridicari masini</t>
         </is>
@@ -13390,11 +13362,7 @@
       <c r="E378" t="n">
         <v>11</v>
       </c>
-      <c r="F378" t="inlineStr">
-        <is>
-          <t>annex</t>
-        </is>
-      </c>
+      <c r="F378" t="inlineStr"/>
       <c r="G378" s="3" t="n">
         <v>290000</v>
       </c>
@@ -13569,12 +13537,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>49.02 credite_restante: parent 826.705.000,00 != sum(children) 306.782.000,00 (2 children)</t>
+          <t>49.02 total_2024: parent 604.574.000,00 != sum(children) 85.019.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -13599,12 +13567,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>49.02 total_2024: parent 604.574.000,00 != sum(children) 85.019.000,00 (2 children)</t>
+          <t>49.02 credite_restante: parent 826.705.000,00 != sum(children) 306.782.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -13794,12 +13762,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.02 credite_restante: parent 617.000,00 != sum(children) 600.000,00 (1 children)</t>
+          <t>61.02 total_2024: parent 24.323.000,00 != sum(children) 1.064.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -13824,12 +13792,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.02 total_2024: parent 24.323.000,00 != sum(children) 1.064.000,00 (1 children)</t>
+          <t>61.02 credite_restante: parent 617.000,00 != sum(children) 600.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -13909,12 +13877,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>65.02 credite_restante: parent 169.303.000,00 != sum(children) 34.950.000,00 (1 children)</t>
+          <t>65.02 total_2024: parent 88.907.000,00 != sum(children) 9.123.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -13939,12 +13907,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>65.02 total_2024: parent 88.907.000,00 != sum(children) 9.123.000,00 (1 children)</t>
+          <t>65.02 credite_restante: parent 169.303.000,00 != sum(children) 34.950.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -14214,12 +14182,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>70.02 credite_restante: parent 275.712.000,00 != sum(children) 211.955.000,00 (1 children)</t>
+          <t>70.02 total_2024: parent 95.045.000,00 != sum(children) 30.658.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -14244,12 +14212,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>70.02 total_2024: parent 95.045.000,00 != sum(children) 30.658.000,00 (1 children)</t>
+          <t>70.02 credite_restante: parent 275.712.000,00 != sum(children) 211.955.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -14474,12 +14442,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>74.02 credite_restante: parent 162.000.000,00 != sum(children) 2.000.000,00 (1 children)</t>
+          <t>74.02 total_2024: parent 59.308.000,00 != sum(children) 1.500.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -14504,12 +14472,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>74.02 total_2024: parent 59.308.000,00 != sum(children) 1.500.000,00 (1 children)</t>
+          <t>74.02 credite_restante: parent 162.000.000,00 != sum(children) 2.000.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -14584,12 +14552,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>84.02 credite_restante: parent 215.048.000,00 != sum(children) 55.912.000,00 (2 children)</t>
+          <t>84.02 total_2024: parent 121.708.000,00 != sum(children) 31.465.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -14614,12 +14582,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>84.02 total_2024: parent 121.708.000,00 != sum(children) 31.465.000,00 (2 children)</t>
+          <t>84.02 credite_restante: parent 215.048.000,00 != sum(children) 55.912.000,00 (2 children)</t>
         </is>
       </c>
     </row>
@@ -14669,12 +14637,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>credite_restante</t>
+          <t>total_2024</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>84.02.03 credite_restante: parent 215.048.000,00 != sum(children) 77.040.000,00 (1 children)</t>
+          <t>84.02.03 total_2024: parent 121.708.000,00 != sum(children) 50.117.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -14699,12 +14667,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>total_2024</t>
+          <t>credite_restante</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>84.02.03 total_2024: parent 121.708.000,00 != sum(children) 50.117.000,00 (1 children)</t>
+          <t>84.02.03 credite_restante: parent 215.048.000,00 != sum(children) 77.040.000,00 (1 children)</t>
         </is>
       </c>
     </row>
@@ -14719,7 +14687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B26"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14745,7 +14713,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -14789,7 +14757,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>374</v>
+        <v>366</v>
       </c>
     </row>
     <row r="7">
@@ -14799,7 +14767,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>339</v>
+        <v>331</v>
       </c>
     </row>
     <row r="8">
@@ -14809,7 +14777,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>90.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -14845,27 +14813,27 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Pagini asteptate</t>
+          <t>Linii anexe separate</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Pagini selectate</t>
+          <t>Celule numerice anexe separate</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>Pagini procesate</t>
+          <t>Pagini asteptate</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -14875,115 +14843,111 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>PDF complet</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>da</t>
-        </is>
+          <t>Pagini selectate</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>Linii fara probleme</t>
+          <t>Pagini procesate</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>339</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>% curat</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>90.59999999999999</v>
+          <t>PDF complet</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>Erori</t>
+          <t>Linii fara probleme</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>30</v>
+        <v>331</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Avertismente</t>
+          <t>% curat</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>90.40000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>Informatii</t>
+          <t>Erori</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Schema publicare</t>
+          <t>Avertismente</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="inlineStr">
         <is>
-          <t>Bundle conversie</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>8b5eded1ef643ad9a06e92cf</t>
-        </is>
+          <t>Informatii</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>SHA-256 sursa</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>d57cfed1bfb05a9c8d63dd4e71007e3c8a89ad5c58460959643ab57e8ec43f01</t>
-        </is>
+          <t>Schema publicare</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>Format sursa</t>
+          <t>Bundle conversie</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pdf</t>
+          <t>32e0a9eced2a389ac2eb0814</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>SHA-256 PDF sursa</t>
+          <t>SHA-256 sursa</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -14995,10 +14959,34 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
+          <t>Format sursa</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>SHA-256 PDF sursa</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>d57cfed1bfb05a9c8d63dd4e71007e3c8a89ad5c58460959643ab57e8ec43f01</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
           <t xml:space="preserve">— BUGETUL LOCAL DETALIAT LA VENITURI PE CAPITOLE, SUBCAPITOLE </t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>local, pag. 1-11, 379 linii</t>
         </is>
